--- a/AAII_Financials/Quarterly/FFLO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFLO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
   <si>
     <t>FFLO</t>
   </si>
@@ -656,136 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -799,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <v>100</v>
@@ -811,32 +815,32 @@
         <v>100</v>
       </c>
       <c r="K8" s="3">
+        <v>100</v>
+      </c>
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
-        <v>100</v>
-      </c>
       <c r="O8" s="3">
         <v>100</v>
       </c>
       <c r="P8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
-        <v>100</v>
-      </c>
       <c r="R8" s="3">
+        <v>100</v>
+      </c>
+      <c r="S8" s="3">
         <v>200</v>
       </c>
-      <c r="S8" s="3">
-        <v>100</v>
-      </c>
       <c r="T8" s="3">
         <v>100</v>
       </c>
@@ -847,7 +851,7 @@
         <v>100</v>
       </c>
       <c r="W8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
@@ -859,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="AA8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
         <v>100</v>
@@ -873,8 +877,11 @@
       <c r="AE8" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -891,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
         <v>100</v>
@@ -903,22 +910,22 @@
         <v>100</v>
       </c>
       <c r="L9" s="3">
+        <v>100</v>
+      </c>
+      <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="M9" s="3">
-        <v>100</v>
-      </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3">
         <v>100</v>
       </c>
       <c r="Q9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9" s="3">
         <v>0</v>
@@ -927,10 +934,10 @@
         <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9" s="3">
         <v>0</v>
@@ -948,22 +955,25 @@
         <v>0</v>
       </c>
       <c r="AA9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC9" s="3">
         <v>0</v>
       </c>
       <c r="AD9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3">
         <v>-100</v>
       </c>
-      <c r="AE9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -977,10 +987,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
@@ -989,43 +999,43 @@
         <v>0</v>
       </c>
       <c r="K10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3">
+        <v>100</v>
+      </c>
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="M10" s="3">
-        <v>100</v>
-      </c>
       <c r="N10" s="3">
         <v>100</v>
       </c>
       <c r="O10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3">
         <v>100</v>
       </c>
       <c r="R10" s="3">
+        <v>100</v>
+      </c>
+      <c r="S10" s="3">
         <v>200</v>
       </c>
-      <c r="S10" s="3">
-        <v>100</v>
-      </c>
       <c r="T10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V10" s="3">
         <v>100</v>
       </c>
       <c r="W10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X10" s="3">
         <v>0</v>
@@ -1040,19 +1050,22 @@
         <v>0</v>
       </c>
       <c r="AB10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="3">
         <v>100</v>
       </c>
       <c r="AD10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE10" s="3">
         <v>200</v>
       </c>
-      <c r="AE10" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,19 +1279,22 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1282,23 +1302,23 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3">
-        <v>-300</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3">
+        <v>-300</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
@@ -1309,8 +1329,8 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1336,8 +1356,8 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>4</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>4</v>
@@ -1345,14 +1365,17 @@
       <c r="AC14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1412,8 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>4</v>
@@ -1407,14 +1430,14 @@
       <c r="T15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>4</v>
@@ -1422,8 +1445,8 @@
       <c r="Y15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,79 +1496,80 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
       </c>
       <c r="F17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G17" s="3">
         <v>100</v>
       </c>
       <c r="H17" s="3">
+        <v>100</v>
+      </c>
+      <c r="I17" s="3">
         <v>200</v>
       </c>
-      <c r="I17" s="3">
-        <v>100</v>
-      </c>
       <c r="J17" s="3">
+        <v>100</v>
+      </c>
+      <c r="K17" s="3">
         <v>-100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>200</v>
       </c>
-      <c r="L17" s="3">
-        <v>100</v>
-      </c>
       <c r="M17" s="3">
+        <v>100</v>
+      </c>
+      <c r="N17" s="3">
         <v>-200</v>
-      </c>
-      <c r="N17" s="3">
-        <v>200</v>
       </c>
       <c r="O17" s="3">
         <v>200</v>
       </c>
       <c r="P17" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q17" s="3">
         <v>100</v>
       </c>
       <c r="R17" s="3">
+        <v>100</v>
+      </c>
+      <c r="S17" s="3">
         <v>200</v>
       </c>
-      <c r="S17" s="3">
-        <v>100</v>
-      </c>
       <c r="T17" s="3">
+        <v>100</v>
+      </c>
+      <c r="U17" s="3">
         <v>300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>200</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
       <c r="W17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y17" s="3">
         <v>0</v>
       </c>
       <c r="Z17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3">
         <v>100</v>
@@ -1559,8 +1586,11 @@
       <c r="AE17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1571,40 +1601,40 @@
         <v>0</v>
       </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
       <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
         <v>300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>400</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-100</v>
       </c>
       <c r="O18" s="3">
         <v>-100</v>
       </c>
       <c r="P18" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="Q18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18" s="3">
         <v>0</v>
@@ -1613,29 +1643,29 @@
         <v>0</v>
       </c>
       <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
-        <v>100</v>
-      </c>
       <c r="W18" s="3">
+        <v>100</v>
+      </c>
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
         <v>0</v>
       </c>
       <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-100</v>
       </c>
-      <c r="AA18" s="3">
-        <v>0</v>
-      </c>
       <c r="AB18" s="3">
         <v>0</v>
       </c>
@@ -1648,8 +1678,11 @@
       <c r="AE18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1702,11 +1736,11 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2600</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1717,13 +1751,13 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="O20" s="3">
-        <v>100</v>
-      </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1735,19 +1769,19 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
@@ -1770,8 +1804,11 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1802,12 +1839,12 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>400</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1826,12 +1863,12 @@
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>-100</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1859,8 +1896,11 @@
       <c r="AE21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1948,70 +1988,73 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
       </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
         <v>-100</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>200</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M23" s="3">
         <v>400</v>
       </c>
       <c r="N23" s="3">
+        <v>400</v>
+      </c>
+      <c r="O23" s="3">
         <v>800</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U23" s="3">
         <v>-100</v>
       </c>
       <c r="V23" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="W23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X23" s="3">
         <v>0</v>
@@ -2020,11 +2063,11 @@
         <v>0</v>
       </c>
       <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-100</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
       <c r="AB23" s="3">
         <v>0</v>
       </c>
@@ -2037,8 +2080,11 @@
       <c r="AE23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,70 +2264,73 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E26" s="3">
         <v>0</v>
       </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>200</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M26" s="3">
         <v>400</v>
       </c>
       <c r="N26" s="3">
+        <v>400</v>
+      </c>
+      <c r="O26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U26" s="3">
         <v>-100</v>
       </c>
       <c r="V26" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="W26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X26" s="3">
         <v>0</v>
@@ -2287,11 +2339,11 @@
         <v>0</v>
       </c>
       <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
       <c r="AB26" s="3">
         <v>0</v>
       </c>
@@ -2304,70 +2356,73 @@
       <c r="AE26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E27" s="3">
         <v>0</v>
       </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>200</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M27" s="3">
         <v>400</v>
       </c>
       <c r="N27" s="3">
+        <v>400</v>
+      </c>
+      <c r="O27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U27" s="3">
         <v>-100</v>
       </c>
       <c r="V27" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="W27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X27" s="3">
         <v>0</v>
@@ -2376,11 +2431,11 @@
         <v>0</v>
       </c>
       <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
       <c r="AB27" s="3">
         <v>0</v>
       </c>
@@ -2393,8 +2448,11 @@
       <c r="AE27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2770,11 +2840,11 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>2600</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2785,14 +2855,14 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2803,20 +2873,20 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2838,70 +2908,73 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E33" s="3">
         <v>0</v>
       </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>200</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M33" s="3">
         <v>400</v>
       </c>
       <c r="N33" s="3">
+        <v>400</v>
+      </c>
+      <c r="O33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U33" s="3">
         <v>-100</v>
       </c>
       <c r="V33" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="W33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X33" s="3">
         <v>0</v>
@@ -2910,11 +2983,11 @@
         <v>0</v>
       </c>
       <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
       <c r="AB33" s="3">
         <v>0</v>
       </c>
@@ -2927,8 +3000,11 @@
       <c r="AE33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,70 +3092,73 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
       </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>200</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M35" s="3">
         <v>400</v>
       </c>
       <c r="N35" s="3">
+        <v>400</v>
+      </c>
+      <c r="O35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3">
         <v>-100</v>
       </c>
       <c r="V35" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="W35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X35" s="3">
         <v>0</v>
@@ -3088,11 +3167,11 @@
         <v>0</v>
       </c>
       <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
       <c r="AB35" s="3">
         <v>0</v>
       </c>
@@ -3105,102 +3184,108 @@
       <c r="AE35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,8 +3351,9 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3283,14 +3370,14 @@
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3">
+        <v>100</v>
+      </c>
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
       <c r="K41" s="3">
         <v>0</v>
       </c>
@@ -3298,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N41" s="3">
         <v>100</v>
@@ -3307,11 +3394,11 @@
         <v>100</v>
       </c>
       <c r="P41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q41" s="3">
         <v>200</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
       <c r="R41" s="3">
         <v>0</v>
       </c>
@@ -3354,8 +3441,11 @@
       <c r="AE41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3533,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3458,11 +3551,11 @@
         <v>100</v>
       </c>
       <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
-        <v>100</v>
-      </c>
       <c r="I43" s="3">
         <v>100</v>
       </c>
@@ -3470,7 +3563,7 @@
         <v>100</v>
       </c>
       <c r="K43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L43" s="3">
         <v>200</v>
@@ -3488,13 +3581,13 @@
         <v>200</v>
       </c>
       <c r="Q43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R43" s="3">
         <v>100</v>
       </c>
       <c r="S43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3556,28 +3652,28 @@
         <v>0</v>
       </c>
       <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
         <v>2500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2300</v>
-      </c>
-      <c r="M44" s="3">
-        <v>1800</v>
       </c>
       <c r="N44" s="3">
         <v>1800</v>
       </c>
       <c r="O44" s="3">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="P44" s="3">
         <v>900</v>
       </c>
       <c r="Q44" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="R44" s="3">
         <v>800</v>
@@ -3586,19 +3682,19 @@
         <v>800</v>
       </c>
       <c r="T44" s="3">
+        <v>800</v>
+      </c>
+      <c r="U44" s="3">
         <v>700</v>
-      </c>
-      <c r="U44" s="3">
-        <v>600</v>
       </c>
       <c r="V44" s="3">
         <v>600</v>
       </c>
       <c r="W44" s="3">
+        <v>600</v>
+      </c>
+      <c r="X44" s="3">
         <v>400</v>
-      </c>
-      <c r="X44" s="3">
-        <v>200</v>
       </c>
       <c r="Y44" s="3">
         <v>200</v>
@@ -3613,16 +3709,19 @@
         <v>200</v>
       </c>
       <c r="AC44" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD44" s="3">
         <v>300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>200</v>
       </c>
-      <c r="AE44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3635,8 +3734,8 @@
       <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
+      <c r="G45" s="3">
+        <v>100</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
@@ -3647,26 +3746,26 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
       <c r="M45" s="3">
-        <v>100</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>100</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -3677,11 +3776,11 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V45" s="3">
-        <v>0</v>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -3689,11 +3788,11 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>0</v>
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
@@ -3705,13 +3804,16 @@
         <v>0</v>
       </c>
       <c r="AD45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3725,61 +3827,61 @@
         <v>200</v>
       </c>
       <c r="G46" s="3">
+        <v>200</v>
+      </c>
+      <c r="H46" s="3">
         <v>300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2500</v>
-      </c>
-      <c r="M46" s="3">
-        <v>2100</v>
       </c>
       <c r="N46" s="3">
         <v>2100</v>
       </c>
       <c r="O46" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P46" s="3">
         <v>1200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1000</v>
-      </c>
-      <c r="R46" s="3">
-        <v>900</v>
       </c>
       <c r="S46" s="3">
         <v>900</v>
       </c>
       <c r="T46" s="3">
+        <v>900</v>
+      </c>
+      <c r="U46" s="3">
         <v>800</v>
-      </c>
-      <c r="U46" s="3">
-        <v>600</v>
       </c>
       <c r="V46" s="3">
         <v>600</v>
       </c>
       <c r="W46" s="3">
+        <v>600</v>
+      </c>
+      <c r="X46" s="3">
         <v>500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>300</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>200</v>
       </c>
       <c r="Z46" s="3">
         <v>200</v>
@@ -3788,7 +3890,7 @@
         <v>200</v>
       </c>
       <c r="AB46" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC46" s="3">
         <v>300</v>
@@ -3797,10 +3899,13 @@
         <v>300</v>
       </c>
       <c r="AE46" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF46" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,8 +3993,11 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3903,7 +4011,7 @@
         <v>500</v>
       </c>
       <c r="G48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="H48" s="3">
         <v>600</v>
@@ -3912,10 +4020,10 @@
         <v>600</v>
       </c>
       <c r="J48" s="3">
+        <v>600</v>
+      </c>
+      <c r="K48" s="3">
         <v>1500</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1600</v>
       </c>
       <c r="L48" s="3">
         <v>1600</v>
@@ -3927,7 +4035,7 @@
         <v>1600</v>
       </c>
       <c r="O48" s="3">
-        <v>700</v>
+        <v>1600</v>
       </c>
       <c r="P48" s="3">
         <v>700</v>
@@ -3939,7 +4047,7 @@
         <v>700</v>
       </c>
       <c r="S48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="T48" s="3">
         <v>800</v>
@@ -3951,10 +4059,10 @@
         <v>800</v>
       </c>
       <c r="W48" s="3">
-        <v>0</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>4</v>
+        <v>800</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>4</v>
@@ -3971,14 +4079,17 @@
       <c r="AC48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD48" s="3">
-        <v>0</v>
+      <c r="AD48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4297,17 +4417,17 @@
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -4321,8 +4441,8 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
+      <c r="AB52" s="3">
+        <v>0</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>4</v>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,8 +4545,11 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4437,40 +4563,40 @@
         <v>700</v>
       </c>
       <c r="G54" s="3">
+        <v>700</v>
+      </c>
+      <c r="H54" s="3">
         <v>900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4100</v>
-      </c>
-      <c r="M54" s="3">
-        <v>3700</v>
       </c>
       <c r="N54" s="3">
         <v>3700</v>
       </c>
       <c r="O54" s="3">
+        <v>3700</v>
+      </c>
+      <c r="P54" s="3">
         <v>1900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1700</v>
-      </c>
-      <c r="R54" s="3">
-        <v>1600</v>
       </c>
       <c r="S54" s="3">
         <v>1600</v>
@@ -4479,19 +4605,19 @@
         <v>1600</v>
       </c>
       <c r="U54" s="3">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="V54" s="3">
         <v>1400</v>
       </c>
       <c r="W54" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X54" s="3">
         <v>500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>300</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>200</v>
       </c>
       <c r="Z54" s="3">
         <v>200</v>
@@ -4500,7 +4626,7 @@
         <v>200</v>
       </c>
       <c r="AB54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC54" s="3">
         <v>300</v>
@@ -4509,10 +4635,13 @@
         <v>300</v>
       </c>
       <c r="AE54" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF54" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,13 +4707,14 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
@@ -4622,10 +4753,10 @@
         <v>0</v>
       </c>
       <c r="Q57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -4642,11 +4773,11 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>0</v>
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z57" s="3">
         <v>0</v>
@@ -4661,13 +4792,16 @@
         <v>0</v>
       </c>
       <c r="AD57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4690,10 +4824,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>1000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>900</v>
       </c>
       <c r="L58" s="3">
         <v>900</v>
@@ -4705,7 +4839,7 @@
         <v>900</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4723,25 +4857,25 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>300</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>200</v>
       </c>
       <c r="Z58" s="3">
         <v>200</v>
       </c>
       <c r="AA58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB58" s="3">
         <v>100</v>
@@ -4755,8 +4889,11 @@
       <c r="AE58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4793,8 +4930,8 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -4814,23 +4951,23 @@
       <c r="U59" s="3">
         <v>0</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3">
-        <v>0</v>
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
+      <c r="Y59" s="3">
+        <v>0</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB59" s="3">
         <v>0</v>
@@ -4838,19 +4975,22 @@
       <c r="AC59" s="3">
         <v>0</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
+      <c r="AD59" s="3">
+        <v>0</v>
       </c>
       <c r="AE59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E60" s="3">
         <v>0</v>
@@ -4868,7 +5008,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K60" s="3">
         <v>1000</v>
@@ -4883,16 +5023,16 @@
         <v>1000</v>
       </c>
       <c r="O60" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
       <c r="Q60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S60" s="3">
         <v>0</v>
@@ -4901,19 +5041,19 @@
         <v>0</v>
       </c>
       <c r="U60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W60" s="3">
         <v>0</v>
       </c>
       <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
         <v>300</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>200</v>
       </c>
       <c r="Z60" s="3">
         <v>200</v>
@@ -4933,8 +5073,11 @@
       <c r="AE60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4957,10 +5100,10 @@
         <v>1700</v>
       </c>
       <c r="J61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K61" s="3">
         <v>1400</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1500</v>
       </c>
       <c r="L61" s="3">
         <v>1500</v>
@@ -4978,7 +5121,7 @@
         <v>1500</v>
       </c>
       <c r="Q61" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="R61" s="3">
         <v>1200</v>
@@ -4987,16 +5130,16 @@
         <v>1200</v>
       </c>
       <c r="T61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U61" s="3">
         <v>1100</v>
-      </c>
-      <c r="U61" s="3">
-        <v>900</v>
       </c>
       <c r="V61" s="3">
         <v>900</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5039,8 +5185,8 @@
       <c r="G62" s="3">
         <v>0</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
+      <c r="H62" s="3">
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
@@ -5051,17 +5197,17 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
@@ -5078,41 +5224,44 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X62" s="3">
         <v>500</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
+      <c r="AD62" s="3">
+        <v>0</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,13 +5533,16 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="E66" s="3">
         <v>1700</v>
@@ -5399,10 +5557,10 @@
         <v>1700</v>
       </c>
       <c r="I66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J66" s="3">
         <v>1800</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2400</v>
       </c>
       <c r="K66" s="3">
         <v>2400</v>
@@ -5411,22 +5569,22 @@
         <v>2400</v>
       </c>
       <c r="M66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N66" s="3">
         <v>2500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2400</v>
-      </c>
-      <c r="O66" s="3">
-        <v>1500</v>
       </c>
       <c r="P66" s="3">
         <v>1500</v>
       </c>
       <c r="Q66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R66" s="3">
         <v>1300</v>
-      </c>
-      <c r="R66" s="3">
-        <v>1200</v>
       </c>
       <c r="S66" s="3">
         <v>1200</v>
@@ -5435,19 +5593,19 @@
         <v>1200</v>
       </c>
       <c r="U66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V66" s="3">
         <v>1000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>300</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>200</v>
       </c>
       <c r="Z66" s="3">
         <v>200</v>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5741,7 +5909,7 @@
         <v>800</v>
       </c>
       <c r="W70" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="X70" s="3">
         <v>300</v>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,13 +6027,16 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="E72" s="3">
         <v>-1900</v>
@@ -5871,7 +6045,7 @@
         <v>-1900</v>
       </c>
       <c r="G72" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="H72" s="3">
         <v>-1800</v>
@@ -5880,22 +6054,22 @@
         <v>-1800</v>
       </c>
       <c r="J72" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K72" s="3">
         <v>800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>700</v>
-      </c>
-      <c r="M72" s="3">
-        <v>300</v>
       </c>
       <c r="N72" s="3">
         <v>300</v>
       </c>
       <c r="O72" s="3">
-        <v>-500</v>
+        <v>300</v>
       </c>
       <c r="P72" s="3">
         <v>-500</v>
@@ -5904,10 +6078,10 @@
         <v>-500</v>
       </c>
       <c r="R72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S72" s="3">
         <v>-600</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-500</v>
       </c>
       <c r="T72" s="3">
         <v>-500</v>
@@ -5916,37 +6090,40 @@
         <v>-500</v>
       </c>
       <c r="V72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W72" s="3">
         <v>-400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-500</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-400</v>
       </c>
       <c r="Y72" s="3">
         <v>-400</v>
       </c>
       <c r="Z72" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA72" s="3">
-        <v>-400</v>
       </c>
       <c r="AB72" s="3">
         <v>-400</v>
       </c>
       <c r="AC72" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD72" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>-400</v>
       </c>
       <c r="AE72" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,13 +6395,16 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="E76" s="3">
         <v>-1800</v>
@@ -6227,37 +6413,37 @@
         <v>-1800</v>
       </c>
       <c r="G76" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="H76" s="3">
         <v>-1700</v>
       </c>
       <c r="I76" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J76" s="3">
         <v>-1600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>900</v>
-      </c>
-      <c r="M76" s="3">
-        <v>500</v>
       </c>
       <c r="N76" s="3">
         <v>500</v>
       </c>
       <c r="O76" s="3">
-        <v>-300</v>
+        <v>500</v>
       </c>
       <c r="P76" s="3">
         <v>-300</v>
       </c>
       <c r="Q76" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="R76" s="3">
         <v>-400</v>
@@ -6272,7 +6458,7 @@
         <v>-400</v>
       </c>
       <c r="V76" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="W76" s="3">
         <v>-300</v>
@@ -6290,19 +6476,22 @@
         <v>-300</v>
       </c>
       <c r="AB76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AC76" s="3">
         <v>-200</v>
       </c>
       <c r="AD76" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AE76" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,164 +6579,170 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E81" s="3">
         <v>0</v>
       </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>200</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M81" s="3">
         <v>400</v>
       </c>
       <c r="N81" s="3">
+        <v>400</v>
+      </c>
+      <c r="O81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U81" s="3">
         <v>-100</v>
       </c>
       <c r="V81" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="W81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X81" s="3">
         <v>0</v>
@@ -6556,11 +6751,11 @@
         <v>0</v>
       </c>
       <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
       <c r="AB81" s="3">
         <v>0</v>
       </c>
@@ -6573,8 +6768,11 @@
       <c r="AE81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,8 +7354,11 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7155,7 +7372,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
         <v>-100</v>
@@ -7164,7 +7381,7 @@
         <v>-100</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -7179,35 +7396,35 @@
         <v>0</v>
       </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R89" s="3">
         <v>-100</v>
       </c>
       <c r="S89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
         <v>0</v>
       </c>
@@ -7224,13 +7441,16 @@
         <v>0</v>
       </c>
       <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,25 +7756,28 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>0</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>4</v>
@@ -7564,8 +7794,8 @@
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8028,11 +8274,11 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -8043,38 +8289,38 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>100</v>
-      </c>
       <c r="R100" s="3">
         <v>100</v>
       </c>
       <c r="S100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>300</v>
       </c>
-      <c r="U100" s="3">
-        <v>100</v>
-      </c>
       <c r="V100" s="3">
         <v>100</v>
       </c>
       <c r="W100" s="3">
+        <v>100</v>
+      </c>
+      <c r="X100" s="3">
         <v>300</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
@@ -8091,13 +8337,16 @@
         <v>0</v>
       </c>
       <c r="AD100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,8 +8434,11 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8200,17 +8452,17 @@
         <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>-100</v>
       </c>
       <c r="I102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
@@ -8224,14 +8476,14 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
@@ -8272,6 +8524,9 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FFLO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFLO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
   <si>
     <t>FFLO</t>
   </si>
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -806,10 +813,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <v>100</v>
@@ -818,22 +825,22 @@
         <v>100</v>
       </c>
       <c r="L8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M8" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="N8" s="3">
         <v>200</v>
       </c>
       <c r="O8" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="P8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R8" s="3">
         <v>100</v>
@@ -845,7 +852,7 @@
         <v>100</v>
       </c>
       <c r="U8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V8" s="3">
         <v>100</v>
@@ -854,10 +861,10 @@
         <v>100</v>
       </c>
       <c r="X8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
@@ -866,10 +873,10 @@
         <v>0</v>
       </c>
       <c r="AB8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
         <v>100</v>
@@ -880,8 +887,14 @@
       <c r="AF8" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -901,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3">
         <v>100</v>
@@ -913,37 +926,37 @@
         <v>100</v>
       </c>
       <c r="M9" s="3">
+        <v>100</v>
+      </c>
+      <c r="N9" s="3">
+        <v>100</v>
+      </c>
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3">
-        <v>100</v>
-      </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
       <c r="P9" s="3">
         <v>100</v>
       </c>
       <c r="Q9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9" s="3">
         <v>0</v>
       </c>
       <c r="U9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V9" s="3">
         <v>0</v>
       </c>
       <c r="W9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X9" s="3">
         <v>0</v>
@@ -958,22 +971,28 @@
         <v>0</v>
       </c>
       <c r="AB9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="3">
         <v>0</v>
       </c>
       <c r="AD9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="3">
         <v>-100</v>
       </c>
-      <c r="AF9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -990,58 +1009,58 @@
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
       </c>
       <c r="L10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>100</v>
+      </c>
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="N10" s="3">
-        <v>100</v>
-      </c>
-      <c r="O10" s="3">
-        <v>100</v>
-      </c>
       <c r="P10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="3">
         <v>100</v>
       </c>
       <c r="R10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S10" s="3">
+        <v>100</v>
+      </c>
+      <c r="T10" s="3">
+        <v>100</v>
+      </c>
+      <c r="U10" s="3">
         <v>200</v>
       </c>
-      <c r="T10" s="3">
-        <v>100</v>
-      </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
       <c r="V10" s="3">
         <v>100</v>
       </c>
       <c r="W10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z10" s="3">
         <v>0</v>
@@ -1053,19 +1072,25 @@
         <v>0</v>
       </c>
       <c r="AC10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG10" s="3">
         <v>200</v>
       </c>
-      <c r="AF10" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,34 +1315,40 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
@@ -1317,14 +1356,14 @@
       <c r="M14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>-300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
+      <c r="P14" s="3">
+        <v>-300</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
@@ -1332,11 +1371,11 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1359,23 +1398,29 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>4</v>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1415,11 +1460,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>4</v>
@@ -1433,26 +1478,26 @@
       <c r="U15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
+      <c r="V15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,85 +1548,87 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E17" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3">
+        <v>100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>100</v>
+      </c>
+      <c r="K17" s="3">
         <v>200</v>
       </c>
-      <c r="J17" s="3">
-        <v>100</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
+        <v>100</v>
+      </c>
+      <c r="M17" s="3">
         <v>-100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
-        <v>100</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
+        <v>100</v>
+      </c>
+      <c r="P17" s="3">
         <v>-200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
-        <v>100</v>
-      </c>
-      <c r="R17" s="3">
-        <v>100</v>
-      </c>
       <c r="S17" s="3">
+        <v>100</v>
+      </c>
+      <c r="T17" s="3">
+        <v>100</v>
+      </c>
+      <c r="U17" s="3">
         <v>200</v>
       </c>
-      <c r="T17" s="3">
-        <v>100</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
+        <v>100</v>
+      </c>
+      <c r="W17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>200</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3">
-        <v>100</v>
-      </c>
       <c r="Y17" s="3">
         <v>0</v>
       </c>
       <c r="Z17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC17" s="3">
         <v>100</v>
@@ -1589,8 +1642,14 @@
       <c r="AF17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,13 +1657,13 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H18" s="3">
         <v>0</v>
@@ -1616,62 +1675,62 @@
         <v>0</v>
       </c>
       <c r="K18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
         <v>200</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3">
-        <v>100</v>
-      </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T18" s="3">
         <v>0</v>
       </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
         <v>-200</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W18" s="3">
-        <v>100</v>
       </c>
       <c r="X18" s="3">
         <v>-100</v>
       </c>
       <c r="Y18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-100</v>
       </c>
-      <c r="AB18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>0</v>
-      </c>
       <c r="AD18" s="3">
         <v>0</v>
       </c>
@@ -1681,8 +1740,14 @@
       <c r="AF18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1739,14 +1806,14 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-2600</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1754,16 +1821,16 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -1772,22 +1839,22 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
@@ -1807,8 +1874,14 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1842,15 +1915,15 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3">
         <v>400</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1866,15 +1939,15 @@
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3">
         <v>-100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1899,8 +1972,14 @@
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,22 +2070,28 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-100</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3">
         <v>0</v>
@@ -2015,34 +2100,34 @@
         <v>-100</v>
       </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>200</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>800</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>100</v>
-      </c>
       <c r="R23" s="3">
         <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T23" s="3">
         <v>0</v>
@@ -2051,29 +2136,29 @@
         <v>-100</v>
       </c>
       <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
-        <v>100</v>
-      </c>
       <c r="X23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z23" s="3">
         <v>0</v>
       </c>
       <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-100</v>
       </c>
-      <c r="AB23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>0</v>
-      </c>
       <c r="AD23" s="3">
         <v>0</v>
       </c>
@@ -2083,8 +2168,14 @@
       <c r="AF23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,22 +2364,28 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
         <v>0</v>
@@ -2291,34 +2394,34 @@
         <v>-100</v>
       </c>
       <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L26" s="3">
         <v>-2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>200</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>800</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>100</v>
-      </c>
       <c r="R26" s="3">
         <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T26" s="3">
         <v>0</v>
@@ -2327,29 +2430,29 @@
         <v>-100</v>
       </c>
       <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
-        <v>100</v>
-      </c>
       <c r="X26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z26" s="3">
         <v>0</v>
       </c>
       <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-100</v>
       </c>
-      <c r="AB26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>0</v>
-      </c>
       <c r="AD26" s="3">
         <v>0</v>
       </c>
@@ -2359,22 +2462,28 @@
       <c r="AF26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3">
         <v>0</v>
@@ -2383,34 +2492,34 @@
         <v>-100</v>
       </c>
       <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L27" s="3">
         <v>-2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>200</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>800</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>100</v>
-      </c>
       <c r="R27" s="3">
         <v>0</v>
       </c>
       <c r="S27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T27" s="3">
         <v>0</v>
@@ -2419,29 +2528,29 @@
         <v>-100</v>
       </c>
       <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
-        <v>100</v>
-      </c>
       <c r="X27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z27" s="3">
         <v>0</v>
       </c>
       <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-100</v>
       </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>0</v>
-      </c>
       <c r="AD27" s="3">
         <v>0</v>
       </c>
@@ -2451,8 +2560,14 @@
       <c r="AF27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2843,14 +2982,14 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>2600</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2858,17 +2997,17 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2876,23 +3015,23 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -2911,22 +3050,28 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
         <v>0</v>
@@ -2935,34 +3080,34 @@
         <v>-100</v>
       </c>
       <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L33" s="3">
         <v>-2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>200</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>800</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>100</v>
-      </c>
       <c r="R33" s="3">
         <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T33" s="3">
         <v>0</v>
@@ -2971,29 +3116,29 @@
         <v>-100</v>
       </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
-        <v>100</v>
-      </c>
       <c r="X33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z33" s="3">
         <v>0</v>
       </c>
       <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-100</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>0</v>
-      </c>
       <c r="AD33" s="3">
         <v>0</v>
       </c>
@@ -3003,8 +3148,14 @@
       <c r="AF33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,22 +3246,28 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
         <v>0</v>
@@ -3119,34 +3276,34 @@
         <v>-100</v>
       </c>
       <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L35" s="3">
         <v>-2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>200</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>800</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>100</v>
-      </c>
       <c r="R35" s="3">
         <v>0</v>
       </c>
       <c r="S35" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T35" s="3">
         <v>0</v>
@@ -3155,29 +3312,29 @@
         <v>-100</v>
       </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
-        <v>100</v>
-      </c>
       <c r="X35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z35" s="3">
         <v>0</v>
       </c>
       <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-100</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>0</v>
-      </c>
       <c r="AD35" s="3">
         <v>0</v>
       </c>
@@ -3187,105 +3344,117 @@
       <c r="AF35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,8 +3523,10 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3373,38 +3546,38 @@
         <v>0</v>
       </c>
       <c r="I41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
+        <v>100</v>
+      </c>
+      <c r="L41" s="3">
         <v>300</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
       <c r="M41" s="3">
         <v>0</v>
       </c>
       <c r="N41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P41" s="3">
         <v>100</v>
       </c>
       <c r="Q41" s="3">
+        <v>100</v>
+      </c>
+      <c r="R41" s="3">
+        <v>100</v>
+      </c>
+      <c r="S41" s="3">
         <v>200</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
         <v>0</v>
       </c>
@@ -3444,8 +3617,14 @@
       <c r="AF41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,13 +3715,19 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
@@ -3554,22 +3739,22 @@
         <v>100</v>
       </c>
       <c r="H43" s="3">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3">
+        <v>100</v>
+      </c>
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
-        <v>100</v>
-      </c>
-      <c r="J43" s="3">
-        <v>100</v>
-      </c>
       <c r="K43" s="3">
         <v>100</v>
       </c>
       <c r="L43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N43" s="3">
         <v>200</v>
@@ -3584,16 +3769,16 @@
         <v>200</v>
       </c>
       <c r="R43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -3628,8 +3813,14 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3655,52 +3846,52 @@
         <v>0</v>
       </c>
       <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
         <v>2500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>900</v>
-      </c>
-      <c r="R44" s="3">
-        <v>800</v>
-      </c>
-      <c r="S44" s="3">
-        <v>800</v>
       </c>
       <c r="T44" s="3">
         <v>800</v>
       </c>
       <c r="U44" s="3">
+        <v>800</v>
+      </c>
+      <c r="V44" s="3">
+        <v>800</v>
+      </c>
+      <c r="W44" s="3">
         <v>700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>400</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>200</v>
       </c>
       <c r="AA44" s="3">
         <v>200</v>
@@ -3712,24 +3903,30 @@
         <v>200</v>
       </c>
       <c r="AD44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AE44" s="3">
         <v>200</v>
       </c>
       <c r="AF44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
@@ -3737,11 +3934,11 @@
       <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
+      <c r="H45" s="3">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3">
+        <v>100</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
@@ -3749,29 +3946,29 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
-        <v>100</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>100</v>
+        <v>100</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
@@ -3779,26 +3976,26 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>4</v>
+      <c r="V45" s="3">
+        <v>0</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
+      <c r="X45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>4</v>
+      <c r="Z45" s="3">
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
+      <c r="AB45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
@@ -3807,18 +4004,24 @@
         <v>0</v>
       </c>
       <c r="AE45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF45" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E46" s="3">
         <v>200</v>
@@ -3830,82 +4033,88 @@
         <v>200</v>
       </c>
       <c r="H46" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I46" s="3">
         <v>200</v>
       </c>
       <c r="J46" s="3">
+        <v>300</v>
+      </c>
+      <c r="K46" s="3">
+        <v>200</v>
+      </c>
+      <c r="L46" s="3">
         <v>400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>300</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>200</v>
       </c>
       <c r="AB46" s="3">
         <v>200</v>
       </c>
       <c r="AC46" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AD46" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AE46" s="3">
         <v>300</v>
       </c>
       <c r="AF46" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH46" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,13 +4205,19 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3">
         <v>500</v>
@@ -4014,22 +4229,22 @@
         <v>500</v>
       </c>
       <c r="H48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J48" s="3">
         <v>600</v>
       </c>
       <c r="K48" s="3">
+        <v>600</v>
+      </c>
+      <c r="L48" s="3">
+        <v>600</v>
+      </c>
+      <c r="M48" s="3">
         <v>1500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1600</v>
-      </c>
-      <c r="M48" s="3">
-        <v>1600</v>
       </c>
       <c r="N48" s="3">
         <v>1600</v>
@@ -4038,10 +4253,10 @@
         <v>1600</v>
       </c>
       <c r="P48" s="3">
-        <v>700</v>
+        <v>1600</v>
       </c>
       <c r="Q48" s="3">
-        <v>700</v>
+        <v>1600</v>
       </c>
       <c r="R48" s="3">
         <v>700</v>
@@ -4050,10 +4265,10 @@
         <v>700</v>
       </c>
       <c r="T48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="U48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="V48" s="3">
         <v>800</v>
@@ -4062,13 +4277,13 @@
         <v>800</v>
       </c>
       <c r="X48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>4</v>
+        <v>800</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>0</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>4</v>
@@ -4082,14 +4297,20 @@
       <c r="AD48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4420,20 +4659,20 @@
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>4</v>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -4444,11 +4683,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD52" s="3" t="s">
-        <v>4</v>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>0</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>4</v>
@@ -4456,8 +4695,14 @@
       <c r="AF52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,13 +4793,19 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="E54" s="3">
         <v>700</v>
@@ -4566,82 +4817,88 @@
         <v>700</v>
       </c>
       <c r="H54" s="3">
+        <v>700</v>
+      </c>
+      <c r="I54" s="3">
+        <v>700</v>
+      </c>
+      <c r="J54" s="3">
         <v>900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>4200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>4000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>4100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>3700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1700</v>
-      </c>
-      <c r="S54" s="3">
-        <v>1600</v>
-      </c>
-      <c r="T54" s="3">
-        <v>1600</v>
       </c>
       <c r="U54" s="3">
         <v>1600</v>
       </c>
       <c r="V54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="X54" s="3">
         <v>1400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>300</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>200</v>
       </c>
       <c r="AB54" s="3">
         <v>200</v>
       </c>
       <c r="AC54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AD54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AE54" s="3">
         <v>300</v>
       </c>
       <c r="AF54" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG54" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH54" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,19 +4967,21 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G57" s="3">
         <v>0</v>
@@ -4756,13 +5017,13 @@
         <v>0</v>
       </c>
       <c r="R57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
       <c r="T57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -4776,14 +5037,14 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>4</v>
+      <c r="Y57" s="3">
+        <v>0</v>
       </c>
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB57" s="3">
         <v>0</v>
@@ -4795,13 +5056,19 @@
         <v>0</v>
       </c>
       <c r="AE57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4827,13 +5094,13 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>1000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>900</v>
-      </c>
-      <c r="M58" s="3">
-        <v>900</v>
       </c>
       <c r="N58" s="3">
         <v>900</v>
@@ -4842,10 +5109,10 @@
         <v>900</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4860,29 +5127,29 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
       <c r="X58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>200</v>
       </c>
-      <c r="AB58" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>100</v>
-      </c>
       <c r="AD58" s="3">
         <v>100</v>
       </c>
@@ -4892,8 +5159,14 @@
       <c r="AF58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4933,11 +5206,11 @@
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -4954,49 +5227,55 @@
       <c r="V59" s="3">
         <v>0</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>4</v>
+      <c r="W59" s="3">
+        <v>0</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G60" s="3">
         <v>0</v>
@@ -5011,10 +5290,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L60" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M60" s="3">
         <v>1000</v>
@@ -5026,40 +5305,40 @@
         <v>1000</v>
       </c>
       <c r="P60" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Q60" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S60" s="3">
         <v>0</v>
       </c>
       <c r="T60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U60" s="3">
         <v>0</v>
       </c>
       <c r="V60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W60" s="3">
         <v>0</v>
       </c>
       <c r="X60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="3">
         <v>300</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>200</v>
       </c>
       <c r="AB60" s="3">
         <v>200</v>
@@ -5076,13 +5355,19 @@
       <c r="AF60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1700</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
         <v>1700</v>
@@ -5103,13 +5388,13 @@
         <v>1700</v>
       </c>
       <c r="K61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M61" s="3">
         <v>1400</v>
-      </c>
-      <c r="L61" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M61" s="3">
-        <v>1500</v>
       </c>
       <c r="N61" s="3">
         <v>1500</v>
@@ -5124,29 +5409,29 @@
         <v>1500</v>
       </c>
       <c r="R61" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="S61" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="T61" s="3">
         <v>1200</v>
       </c>
       <c r="U61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W61" s="3">
         <v>1100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>900</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5168,8 +5453,14 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5188,11 +5479,11 @@
       <c r="H62" s="3">
         <v>0</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
@@ -5200,8 +5491,8 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
@@ -5212,8 +5503,8 @@
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
@@ -5227,41 +5518,47 @@
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z62" s="3">
         <v>500</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>0</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,19 +5845,25 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F66" s="3">
         <v>1800</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1700</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1700</v>
       </c>
       <c r="G66" s="3">
         <v>1700</v>
@@ -5560,58 +5875,58 @@
         <v>1700</v>
       </c>
       <c r="J66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L66" s="3">
         <v>1800</v>
-      </c>
-      <c r="K66" s="3">
-        <v>2400</v>
-      </c>
-      <c r="L66" s="3">
-        <v>2400</v>
       </c>
       <c r="M66" s="3">
         <v>2400</v>
       </c>
       <c r="N66" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="O66" s="3">
         <v>2400</v>
       </c>
       <c r="P66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="R66" s="3">
         <v>1500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1300</v>
-      </c>
-      <c r="S66" s="3">
-        <v>1200</v>
-      </c>
-      <c r="T66" s="3">
-        <v>1200</v>
       </c>
       <c r="U66" s="3">
         <v>1200</v>
       </c>
       <c r="V66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X66" s="3">
         <v>1000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>300</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>200</v>
       </c>
       <c r="AB66" s="3">
         <v>200</v>
@@ -5628,8 +5943,14 @@
       <c r="AF66" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH66" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5912,10 +6247,10 @@
         <v>800</v>
       </c>
       <c r="X70" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="Y70" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="Z70" s="3">
         <v>300</v>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,70 +6371,76 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-2000</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-1900</v>
       </c>
       <c r="G72" s="3">
         <v>-1900</v>
       </c>
       <c r="H72" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="I72" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="J72" s="3">
         <v>-1800</v>
       </c>
       <c r="K72" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L72" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M72" s="3">
         <v>800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>300</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-500</v>
       </c>
       <c r="R72" s="3">
         <v>-500</v>
       </c>
       <c r="S72" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="T72" s="3">
         <v>-500</v>
       </c>
       <c r="U72" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="V72" s="3">
         <v>-500</v>
       </c>
       <c r="W72" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="X72" s="3">
         <v>-500</v>
@@ -6102,28 +6449,34 @@
         <v>-400</v>
       </c>
       <c r="Z72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-400</v>
-      </c>
-      <c r="AA72" s="3">
-        <v>-500</v>
       </c>
       <c r="AB72" s="3">
         <v>-400</v>
       </c>
       <c r="AC72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD72" s="3">
         <v>-400</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>-300</v>
       </c>
       <c r="AE72" s="3">
         <v>-400</v>
       </c>
       <c r="AF72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG72" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,58 +6763,64 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F76" s="3">
         <v>-1900</v>
-      </c>
-      <c r="E76" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="F76" s="3">
-        <v>-1800</v>
       </c>
       <c r="G76" s="3">
         <v>-1800</v>
       </c>
       <c r="H76" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I76" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J76" s="3">
         <v>-1700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-1700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-1600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-300</v>
-      </c>
-      <c r="R76" s="3">
-        <v>-400</v>
-      </c>
-      <c r="S76" s="3">
-        <v>-400</v>
       </c>
       <c r="T76" s="3">
         <v>-400</v>
@@ -6461,10 +6832,10 @@
         <v>-400</v>
       </c>
       <c r="W76" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="X76" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="Y76" s="3">
         <v>-300</v>
@@ -6479,19 +6850,25 @@
         <v>-300</v>
       </c>
       <c r="AC76" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD76" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AE76" s="3">
         <v>-200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,119 +6959,131 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
         <v>0</v>
@@ -6703,34 +7092,34 @@
         <v>-100</v>
       </c>
       <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L81" s="3">
         <v>-2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>200</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>800</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>100</v>
-      </c>
       <c r="R81" s="3">
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T81" s="3">
         <v>0</v>
@@ -6739,29 +7128,29 @@
         <v>-100</v>
       </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
-        <v>100</v>
-      </c>
       <c r="X81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z81" s="3">
         <v>0</v>
       </c>
       <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-100</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>0</v>
-      </c>
       <c r="AD81" s="3">
         <v>0</v>
       </c>
@@ -6771,8 +7160,14 @@
       <c r="AF81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,13 +7784,19 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
@@ -7375,19 +7808,19 @@
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3">
         <v>-100</v>
       </c>
       <c r="K89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -7399,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="P89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
@@ -7408,29 +7841,29 @@
         <v>-100</v>
       </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
         <v>0</v>
       </c>
@@ -7444,13 +7877,19 @@
         <v>0</v>
       </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7575,8 +8016,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,31 +8212,37 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
+        <v>1700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>4</v>
@@ -7797,11 +8256,11 @@
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -7851,8 +8310,14 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8738,14 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8277,14 +8768,14 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -8292,41 +8783,41 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
-        <v>100</v>
-      </c>
-      <c r="S100" s="3">
-        <v>100</v>
-      </c>
       <c r="T100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U100" s="3">
+        <v>100</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>300</v>
       </c>
-      <c r="V100" s="3">
-        <v>100</v>
-      </c>
-      <c r="W100" s="3">
-        <v>100</v>
-      </c>
       <c r="X100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z100" s="3">
         <v>300</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -8340,13 +8831,19 @@
         <v>0</v>
       </c>
       <c r="AE100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,8 +8934,14 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8455,20 +8958,20 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
@@ -8479,17 +8982,17 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
@@ -8527,6 +9030,12 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FFLO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFLO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
   <si>
     <t>FFLO</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -819,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <v>100</v>
@@ -831,32 +835,32 @@
         <v>100</v>
       </c>
       <c r="N8" s="3">
+        <v>100</v>
+      </c>
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
-        <v>100</v>
-      </c>
       <c r="R8" s="3">
         <v>100</v>
       </c>
       <c r="S8" s="3">
+        <v>100</v>
+      </c>
+      <c r="T8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
-        <v>100</v>
-      </c>
       <c r="U8" s="3">
+        <v>100</v>
+      </c>
+      <c r="V8" s="3">
         <v>200</v>
       </c>
-      <c r="V8" s="3">
-        <v>100</v>
-      </c>
       <c r="W8" s="3">
         <v>100</v>
       </c>
@@ -867,7 +871,7 @@
         <v>100</v>
       </c>
       <c r="Z8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
@@ -879,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="AD8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3">
         <v>100</v>
@@ -893,8 +897,11 @@
       <c r="AH8" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -920,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3">
         <v>100</v>
@@ -932,22 +939,22 @@
         <v>100</v>
       </c>
       <c r="O9" s="3">
+        <v>100</v>
+      </c>
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3">
-        <v>100</v>
-      </c>
       <c r="Q9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3">
         <v>100</v>
       </c>
       <c r="T9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U9" s="3">
         <v>0</v>
@@ -956,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y9" s="3">
         <v>0</v>
@@ -977,22 +984,25 @@
         <v>0</v>
       </c>
       <c r="AD9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF9" s="3">
         <v>0</v>
       </c>
       <c r="AG9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="3">
         <v>-100</v>
       </c>
-      <c r="AH9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,10 +1025,10 @@
         <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
@@ -1027,43 +1037,43 @@
         <v>0</v>
       </c>
       <c r="N10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3">
+        <v>100</v>
+      </c>
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="P10" s="3">
-        <v>100</v>
-      </c>
       <c r="Q10" s="3">
         <v>100</v>
       </c>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T10" s="3">
         <v>100</v>
       </c>
       <c r="U10" s="3">
+        <v>100</v>
+      </c>
+      <c r="V10" s="3">
         <v>200</v>
       </c>
-      <c r="V10" s="3">
-        <v>100</v>
-      </c>
       <c r="W10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3">
         <v>100</v>
       </c>
       <c r="Z10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA10" s="3">
         <v>0</v>
@@ -1078,19 +1088,22 @@
         <v>0</v>
       </c>
       <c r="AE10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="3">
         <v>100</v>
       </c>
       <c r="AG10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH10" s="3">
         <v>200</v>
       </c>
-      <c r="AH10" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,16 +1338,19 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1338,11 +1358,11 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1350,23 +1370,23 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3">
-        <v>-300</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>-300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
+      <c r="Q14" s="3">
+        <v>-300</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
@@ -1377,8 +1397,8 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1404,8 +1424,8 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>4</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>4</v>
@@ -1413,14 +1433,17 @@
       <c r="AF14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1489,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>4</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>4</v>
@@ -1484,14 +1507,14 @@
       <c r="W15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>4</v>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>4</v>
@@ -1499,8 +1522,8 @@
       <c r="AB15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,88 +1576,89 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
         <v>400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>200</v>
       </c>
-      <c r="F17" s="3">
-        <v>100</v>
-      </c>
       <c r="G17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="3">
         <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3">
         <v>100</v>
       </c>
       <c r="K17" s="3">
+        <v>100</v>
+      </c>
+      <c r="L17" s="3">
         <v>200</v>
       </c>
-      <c r="L17" s="3">
-        <v>100</v>
-      </c>
       <c r="M17" s="3">
+        <v>100</v>
+      </c>
+      <c r="N17" s="3">
         <v>-100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
-        <v>100</v>
-      </c>
       <c r="P17" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q17" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>200</v>
       </c>
       <c r="R17" s="3">
         <v>200</v>
       </c>
       <c r="S17" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T17" s="3">
         <v>100</v>
       </c>
       <c r="U17" s="3">
+        <v>100</v>
+      </c>
+      <c r="V17" s="3">
         <v>200</v>
       </c>
-      <c r="V17" s="3">
-        <v>100</v>
-      </c>
       <c r="W17" s="3">
+        <v>100</v>
+      </c>
+      <c r="X17" s="3">
         <v>300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>200</v>
       </c>
-      <c r="Y17" s="3">
-        <v>0</v>
-      </c>
       <c r="Z17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB17" s="3">
         <v>0</v>
       </c>
       <c r="AC17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD17" s="3">
         <v>100</v>
@@ -1648,8 +1675,11 @@
       <c r="AH17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1657,52 +1687,52 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
       <c r="H18" s="3">
         <v>0</v>
       </c>
       <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
       <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
       <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
         <v>300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>400</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-100</v>
       </c>
       <c r="R18" s="3">
         <v>-100</v>
       </c>
       <c r="S18" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="T18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U18" s="3">
         <v>0</v>
@@ -1711,29 +1741,29 @@
         <v>0</v>
       </c>
       <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
-        <v>100</v>
-      </c>
       <c r="Z18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-100</v>
       </c>
-      <c r="AA18" s="3">
-        <v>0</v>
-      </c>
       <c r="AB18" s="3">
         <v>0</v>
       </c>
       <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-100</v>
       </c>
-      <c r="AD18" s="3">
-        <v>0</v>
-      </c>
       <c r="AE18" s="3">
         <v>0</v>
       </c>
@@ -1746,8 +1776,11 @@
       <c r="AH18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1791,7 +1825,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1812,11 +1846,11 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-2600</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1827,13 +1861,13 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
-        <v>100</v>
-      </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1845,19 +1879,19 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
@@ -1880,8 +1914,11 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1921,12 +1958,12 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1945,12 +1982,12 @@
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1978,8 +2015,11 @@
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2076,79 +2116,82 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-100</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
         <v>0</v>
       </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>200</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P23" s="3">
         <v>400</v>
       </c>
       <c r="Q23" s="3">
+        <v>400</v>
+      </c>
+      <c r="R23" s="3">
         <v>800</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X23" s="3">
         <v>-100</v>
       </c>
       <c r="Y23" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="Z23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA23" s="3">
         <v>0</v>
@@ -2157,11 +2200,11 @@
         <v>0</v>
       </c>
       <c r="AC23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-100</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
       <c r="AE23" s="3">
         <v>0</v>
       </c>
@@ -2174,8 +2217,11 @@
       <c r="AH23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,79 +2419,82 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
         <v>0</v>
       </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>200</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P26" s="3">
         <v>400</v>
       </c>
       <c r="Q26" s="3">
+        <v>400</v>
+      </c>
+      <c r="R26" s="3">
         <v>800</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X26" s="3">
         <v>-100</v>
       </c>
       <c r="Y26" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="Z26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA26" s="3">
         <v>0</v>
@@ -2451,11 +2503,11 @@
         <v>0</v>
       </c>
       <c r="AC26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-100</v>
       </c>
-      <c r="AD26" s="3">
-        <v>0</v>
-      </c>
       <c r="AE26" s="3">
         <v>0</v>
       </c>
@@ -2468,79 +2520,82 @@
       <c r="AH26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
         <v>0</v>
       </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>200</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P27" s="3">
         <v>400</v>
       </c>
       <c r="Q27" s="3">
+        <v>400</v>
+      </c>
+      <c r="R27" s="3">
         <v>800</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X27" s="3">
         <v>-100</v>
       </c>
       <c r="Y27" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="Z27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA27" s="3">
         <v>0</v>
@@ -2549,11 +2604,11 @@
         <v>0</v>
       </c>
       <c r="AC27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-100</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
       <c r="AE27" s="3">
         <v>0</v>
       </c>
@@ -2566,8 +2621,11 @@
       <c r="AH27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2967,7 +3037,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2988,11 +3058,11 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>2600</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -3003,14 +3073,14 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -3021,20 +3091,20 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -3056,79 +3126,82 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
         <v>0</v>
       </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>200</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P33" s="3">
         <v>400</v>
       </c>
       <c r="Q33" s="3">
+        <v>400</v>
+      </c>
+      <c r="R33" s="3">
         <v>800</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X33" s="3">
         <v>-100</v>
       </c>
       <c r="Y33" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="Z33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA33" s="3">
         <v>0</v>
@@ -3137,11 +3210,11 @@
         <v>0</v>
       </c>
       <c r="AC33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-100</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
       <c r="AE33" s="3">
         <v>0</v>
       </c>
@@ -3154,8 +3227,11 @@
       <c r="AH33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,79 +3328,82 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
         <v>0</v>
       </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>200</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P35" s="3">
         <v>400</v>
       </c>
       <c r="Q35" s="3">
+        <v>400</v>
+      </c>
+      <c r="R35" s="3">
         <v>800</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X35" s="3">
         <v>-100</v>
       </c>
       <c r="Y35" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="Z35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA35" s="3">
         <v>0</v>
@@ -3333,11 +3412,11 @@
         <v>0</v>
       </c>
       <c r="AC35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-100</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
       <c r="AE35" s="3">
         <v>0</v>
       </c>
@@ -3350,111 +3429,117 @@
       <c r="AH35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,8 +3611,9 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3552,14 +3639,14 @@
         <v>0</v>
       </c>
       <c r="K41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3">
+        <v>100</v>
+      </c>
+      <c r="M41" s="3">
         <v>300</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
       <c r="N41" s="3">
         <v>0</v>
       </c>
@@ -3567,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="3">
         <v>100</v>
@@ -3576,11 +3663,11 @@
         <v>100</v>
       </c>
       <c r="S41" s="3">
+        <v>100</v>
+      </c>
+      <c r="T41" s="3">
         <v>200</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
         <v>0</v>
       </c>
@@ -3623,8 +3710,11 @@
       <c r="AH41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,8 +3811,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3730,7 +3823,7 @@
         <v>400</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
@@ -3745,11 +3838,11 @@
         <v>100</v>
       </c>
       <c r="J43" s="3">
+        <v>100</v>
+      </c>
+      <c r="K43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3">
-        <v>100</v>
-      </c>
       <c r="L43" s="3">
         <v>100</v>
       </c>
@@ -3757,7 +3850,7 @@
         <v>100</v>
       </c>
       <c r="N43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O43" s="3">
         <v>200</v>
@@ -3775,13 +3868,13 @@
         <v>200</v>
       </c>
       <c r="T43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U43" s="3">
         <v>100</v>
       </c>
       <c r="V43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3852,28 +3948,28 @@
         <v>0</v>
       </c>
       <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
         <v>2500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2300</v>
-      </c>
-      <c r="P44" s="3">
-        <v>1800</v>
       </c>
       <c r="Q44" s="3">
         <v>1800</v>
       </c>
       <c r="R44" s="3">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="S44" s="3">
         <v>900</v>
       </c>
       <c r="T44" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="U44" s="3">
         <v>800</v>
@@ -3882,19 +3978,19 @@
         <v>800</v>
       </c>
       <c r="W44" s="3">
+        <v>800</v>
+      </c>
+      <c r="X44" s="3">
         <v>700</v>
-      </c>
-      <c r="X44" s="3">
-        <v>600</v>
       </c>
       <c r="Y44" s="3">
         <v>600</v>
       </c>
       <c r="Z44" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA44" s="3">
         <v>400</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>200</v>
       </c>
       <c r="AB44" s="3">
         <v>200</v>
@@ -3909,16 +4005,19 @@
         <v>200</v>
       </c>
       <c r="AF44" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG44" s="3">
         <v>300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>200</v>
       </c>
-      <c r="AH44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3929,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
@@ -3940,8 +4039,8 @@
       <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
+      <c r="J45" s="3">
+        <v>100</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
@@ -3952,26 +4051,26 @@
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
+      <c r="N45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
       <c r="P45" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>100</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -3982,11 +4081,11 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>0</v>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
@@ -3994,11 +4093,11 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>0</v>
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
@@ -4010,13 +4109,16 @@
         <v>0</v>
       </c>
       <c r="AG45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4024,7 +4126,7 @@
         <v>400</v>
       </c>
       <c r="E46" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F46" s="3">
         <v>200</v>
@@ -4039,61 +4141,61 @@
         <v>200</v>
       </c>
       <c r="J46" s="3">
+        <v>200</v>
+      </c>
+      <c r="K46" s="3">
         <v>300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2500</v>
-      </c>
-      <c r="P46" s="3">
-        <v>2100</v>
       </c>
       <c r="Q46" s="3">
         <v>2100</v>
       </c>
       <c r="R46" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S46" s="3">
         <v>1200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1000</v>
-      </c>
-      <c r="U46" s="3">
-        <v>900</v>
       </c>
       <c r="V46" s="3">
         <v>900</v>
       </c>
       <c r="W46" s="3">
+        <v>900</v>
+      </c>
+      <c r="X46" s="3">
         <v>800</v>
-      </c>
-      <c r="X46" s="3">
-        <v>600</v>
       </c>
       <c r="Y46" s="3">
         <v>600</v>
       </c>
       <c r="Z46" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA46" s="3">
         <v>500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>300</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>200</v>
       </c>
       <c r="AC46" s="3">
         <v>200</v>
@@ -4102,7 +4204,7 @@
         <v>200</v>
       </c>
       <c r="AE46" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF46" s="3">
         <v>300</v>
@@ -4111,10 +4213,13 @@
         <v>300</v>
       </c>
       <c r="AH46" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI46" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,8 +4316,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4220,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3">
         <v>500</v>
@@ -4235,7 +4343,7 @@
         <v>500</v>
       </c>
       <c r="J48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K48" s="3">
         <v>600</v>
@@ -4244,10 +4352,10 @@
         <v>600</v>
       </c>
       <c r="M48" s="3">
+        <v>600</v>
+      </c>
+      <c r="N48" s="3">
         <v>1500</v>
-      </c>
-      <c r="N48" s="3">
-        <v>1600</v>
       </c>
       <c r="O48" s="3">
         <v>1600</v>
@@ -4259,7 +4367,7 @@
         <v>1600</v>
       </c>
       <c r="R48" s="3">
-        <v>700</v>
+        <v>1600</v>
       </c>
       <c r="S48" s="3">
         <v>700</v>
@@ -4271,7 +4379,7 @@
         <v>700</v>
       </c>
       <c r="V48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="W48" s="3">
         <v>800</v>
@@ -4283,10 +4391,10 @@
         <v>800</v>
       </c>
       <c r="Z48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="3" t="s">
-        <v>4</v>
+        <v>800</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>0</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>4</v>
@@ -4303,14 +4411,17 @@
       <c r="AF48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG48" s="3">
-        <v>0</v>
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4665,17 +4785,17 @@
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -4689,8 +4809,8 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
+      <c r="AE52" s="3">
+        <v>0</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>4</v>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,8 +4922,11 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4808,7 +4934,7 @@
         <v>400</v>
       </c>
       <c r="E54" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="F54" s="3">
         <v>700</v>
@@ -4823,40 +4949,40 @@
         <v>700</v>
       </c>
       <c r="J54" s="3">
+        <v>700</v>
+      </c>
+      <c r="K54" s="3">
         <v>900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4100</v>
-      </c>
-      <c r="P54" s="3">
-        <v>3700</v>
       </c>
       <c r="Q54" s="3">
         <v>3700</v>
       </c>
       <c r="R54" s="3">
+        <v>3700</v>
+      </c>
+      <c r="S54" s="3">
         <v>1900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1700</v>
-      </c>
-      <c r="U54" s="3">
-        <v>1600</v>
       </c>
       <c r="V54" s="3">
         <v>1600</v>
@@ -4865,19 +4991,19 @@
         <v>1600</v>
       </c>
       <c r="X54" s="3">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="Y54" s="3">
         <v>1400</v>
       </c>
       <c r="Z54" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AA54" s="3">
         <v>500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>300</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>200</v>
       </c>
       <c r="AC54" s="3">
         <v>200</v>
@@ -4886,7 +5012,7 @@
         <v>200</v>
       </c>
       <c r="AE54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF54" s="3">
         <v>300</v>
@@ -4895,10 +5021,13 @@
         <v>300</v>
       </c>
       <c r="AH54" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI54" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4978,13 +5109,13 @@
         <v>200</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
         <v>0</v>
@@ -5023,10 +5154,10 @@
         <v>0</v>
       </c>
       <c r="T57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -5043,11 +5174,11 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>0</v>
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC57" s="3">
         <v>0</v>
@@ -5062,13 +5193,16 @@
         <v>0</v>
       </c>
       <c r="AG57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5100,10 +5234,10 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>1000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>900</v>
       </c>
       <c r="O58" s="3">
         <v>900</v>
@@ -5115,7 +5249,7 @@
         <v>900</v>
       </c>
       <c r="R58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -5133,25 +5267,25 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>300</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>200</v>
       </c>
       <c r="AC58" s="3">
         <v>200</v>
       </c>
       <c r="AD58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE58" s="3">
         <v>100</v>
@@ -5165,8 +5299,11 @@
       <c r="AH58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5212,8 +5349,8 @@
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
+      <c r="R59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
@@ -5233,23 +5370,23 @@
       <c r="X59" s="3">
         <v>0</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
+      <c r="AB59" s="3">
+        <v>0</v>
       </c>
       <c r="AC59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
@@ -5257,14 +5394,17 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>4</v>
+      <c r="AG59" s="3">
+        <v>0</v>
       </c>
       <c r="AH59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5275,10 +5415,10 @@
         <v>200</v>
       </c>
       <c r="F60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H60" s="3">
         <v>0</v>
@@ -5296,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N60" s="3">
         <v>1000</v>
@@ -5311,16 +5451,16 @@
         <v>1000</v>
       </c>
       <c r="R60" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="S60" s="3">
         <v>0</v>
       </c>
       <c r="T60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V60" s="3">
         <v>0</v>
@@ -5329,19 +5469,19 @@
         <v>0</v>
       </c>
       <c r="X60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z60" s="3">
         <v>0</v>
       </c>
       <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="3">
         <v>300</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>200</v>
       </c>
       <c r="AC60" s="3">
         <v>200</v>
@@ -5361,8 +5501,11 @@
       <c r="AH60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5370,7 +5513,7 @@
         <v>600</v>
       </c>
       <c r="E61" s="3">
-        <v>1700</v>
+        <v>600</v>
       </c>
       <c r="F61" s="3">
         <v>1700</v>
@@ -5394,10 +5537,10 @@
         <v>1700</v>
       </c>
       <c r="M61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N61" s="3">
         <v>1400</v>
-      </c>
-      <c r="N61" s="3">
-        <v>1500</v>
       </c>
       <c r="O61" s="3">
         <v>1500</v>
@@ -5415,7 +5558,7 @@
         <v>1500</v>
       </c>
       <c r="T61" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="U61" s="3">
         <v>1200</v>
@@ -5424,16 +5567,16 @@
         <v>1200</v>
       </c>
       <c r="W61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X61" s="3">
         <v>1100</v>
-      </c>
-      <c r="X61" s="3">
-        <v>900</v>
       </c>
       <c r="Y61" s="3">
         <v>900</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="AA61" s="3">
         <v>0</v>
@@ -5459,8 +5602,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5485,8 +5631,8 @@
       <c r="J62" s="3">
         <v>0</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
+      <c r="K62" s="3">
+        <v>0</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
@@ -5497,17 +5643,17 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
@@ -5524,41 +5670,44 @@
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="X62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA62" s="3">
         <v>500</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>4</v>
+      <c r="AG62" s="3">
+        <v>0</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,8 +6006,11 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5860,13 +6018,13 @@
         <v>800</v>
       </c>
       <c r="E66" s="3">
+        <v>800</v>
+      </c>
+      <c r="F66" s="3">
         <v>1900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1800</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1700</v>
       </c>
       <c r="H66" s="3">
         <v>1700</v>
@@ -5881,10 +6039,10 @@
         <v>1700</v>
       </c>
       <c r="L66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M66" s="3">
         <v>1800</v>
-      </c>
-      <c r="M66" s="3">
-        <v>2400</v>
       </c>
       <c r="N66" s="3">
         <v>2400</v>
@@ -5893,22 +6051,22 @@
         <v>2400</v>
       </c>
       <c r="P66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Q66" s="3">
         <v>2500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2400</v>
-      </c>
-      <c r="R66" s="3">
-        <v>1500</v>
       </c>
       <c r="S66" s="3">
         <v>1500</v>
       </c>
       <c r="T66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U66" s="3">
         <v>1300</v>
-      </c>
-      <c r="U66" s="3">
-        <v>1200</v>
       </c>
       <c r="V66" s="3">
         <v>1200</v>
@@ -5917,19 +6075,19 @@
         <v>1200</v>
       </c>
       <c r="X66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y66" s="3">
         <v>1000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>300</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>200</v>
       </c>
       <c r="AC66" s="3">
         <v>200</v>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6253,7 +6421,7 @@
         <v>800</v>
       </c>
       <c r="Z70" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="AA70" s="3">
         <v>300</v>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,8 +6548,11 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6386,13 +6560,13 @@
         <v>-1300</v>
       </c>
       <c r="E72" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-2200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2000</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-1900</v>
       </c>
       <c r="H72" s="3">
         <v>-1900</v>
@@ -6401,7 +6575,7 @@
         <v>-1900</v>
       </c>
       <c r="J72" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="K72" s="3">
         <v>-1800</v>
@@ -6410,22 +6584,22 @@
         <v>-1800</v>
       </c>
       <c r="M72" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N72" s="3">
         <v>800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>700</v>
-      </c>
-      <c r="P72" s="3">
-        <v>300</v>
       </c>
       <c r="Q72" s="3">
         <v>300</v>
       </c>
       <c r="R72" s="3">
-        <v>-500</v>
+        <v>300</v>
       </c>
       <c r="S72" s="3">
         <v>-500</v>
@@ -6434,10 +6608,10 @@
         <v>-500</v>
       </c>
       <c r="U72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V72" s="3">
         <v>-600</v>
-      </c>
-      <c r="V72" s="3">
-        <v>-500</v>
       </c>
       <c r="W72" s="3">
         <v>-500</v>
@@ -6446,37 +6620,40 @@
         <v>-500</v>
       </c>
       <c r="Y72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA72" s="3">
-        <v>-400</v>
       </c>
       <c r="AB72" s="3">
         <v>-400</v>
       </c>
       <c r="AC72" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD72" s="3">
         <v>-500</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>-400</v>
       </c>
       <c r="AE72" s="3">
         <v>-400</v>
       </c>
       <c r="AF72" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AG72" s="3">
         <v>-300</v>
-      </c>
-      <c r="AG72" s="3">
-        <v>-400</v>
       </c>
       <c r="AH72" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,8 +6952,11 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6778,13 +6964,13 @@
         <v>-1200</v>
       </c>
       <c r="E76" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F76" s="3">
         <v>-2000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1900</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-1800</v>
       </c>
       <c r="H76" s="3">
         <v>-1800</v>
@@ -6793,37 +6979,37 @@
         <v>-1800</v>
       </c>
       <c r="J76" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="K76" s="3">
         <v>-1700</v>
       </c>
       <c r="L76" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="M76" s="3">
         <v>-1600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>900</v>
-      </c>
-      <c r="P76" s="3">
-        <v>500</v>
       </c>
       <c r="Q76" s="3">
         <v>500</v>
       </c>
       <c r="R76" s="3">
-        <v>-300</v>
+        <v>500</v>
       </c>
       <c r="S76" s="3">
         <v>-300</v>
       </c>
       <c r="T76" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="U76" s="3">
         <v>-400</v>
@@ -6838,7 +7024,7 @@
         <v>-400</v>
       </c>
       <c r="Y76" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="Z76" s="3">
         <v>-300</v>
@@ -6856,19 +7042,22 @@
         <v>-300</v>
       </c>
       <c r="AE76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AF76" s="3">
         <v>-200</v>
       </c>
       <c r="AG76" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AH76" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,182 +7154,188 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
         <v>0</v>
       </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>200</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P81" s="3">
         <v>400</v>
       </c>
       <c r="Q81" s="3">
+        <v>400</v>
+      </c>
+      <c r="R81" s="3">
         <v>800</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X81" s="3">
         <v>-100</v>
       </c>
       <c r="Y81" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="Z81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA81" s="3">
         <v>0</v>
@@ -7149,11 +7344,11 @@
         <v>0</v>
       </c>
       <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-100</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
       <c r="AE81" s="3">
         <v>0</v>
       </c>
@@ -7166,8 +7361,11 @@
       <c r="AH81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,17 +8004,20 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1700</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
@@ -7814,7 +8031,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K89" s="3">
         <v>-100</v>
@@ -7823,7 +8040,7 @@
         <v>-100</v>
       </c>
       <c r="M89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -7838,35 +8055,35 @@
         <v>0</v>
       </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U89" s="3">
         <v>-100</v>
       </c>
       <c r="V89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-300</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
       <c r="AB89" s="3">
         <v>0</v>
       </c>
@@ -7883,13 +8100,16 @@
         <v>0</v>
       </c>
       <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-100</v>
       </c>
-      <c r="AH89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,34 +8445,37 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>1700</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
@@ -8262,8 +8492,8 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8774,11 +9020,11 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -8789,38 +9035,38 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>1000</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
-        <v>100</v>
-      </c>
       <c r="U100" s="3">
         <v>100</v>
       </c>
       <c r="V100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>300</v>
       </c>
-      <c r="X100" s="3">
-        <v>100</v>
-      </c>
       <c r="Y100" s="3">
         <v>100</v>
       </c>
       <c r="Z100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA100" s="3">
         <v>300</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
@@ -8837,13 +9083,16 @@
         <v>0</v>
       </c>
       <c r="AG100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,8 +9189,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8964,17 +9216,17 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>-100</v>
       </c>
       <c r="L102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
@@ -8988,14 +9240,14 @@
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
@@ -9036,6 +9288,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
